--- a/request_forms/006_licence_renewal_form--request_forms.xlsx
+++ b/request_forms/006_licence_renewal_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_12345,_'label':_'abc123'}</t>
+          <t>abc123</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 12345, 'label': 'ABC123'}</t>
+          <t>ABC123</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_67890,_'label':_'def456'}</t>
+          <t>def456</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 67890, 'label': 'DEF456'}</t>
+          <t>DEF456</t>
         </is>
       </c>
     </row>
